--- a/Assets/Resources/Stats/Stats/Enemies_stats.xlsx
+++ b/Assets/Resources/Stats/Stats/Enemies_stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linje\EPITA\An-Era-of-the-Seas\Assets\Resources\Stats\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4436A88F-7AC2-4F40-B392-56B2E0356D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E780E0-321E-4BAC-A9C2-9BC1CA702532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Terestrial" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="8">
   <si>
     <t>Level</t>
   </si>
@@ -46,6 +46,21 @@
   </si>
   <si>
     <t>ATK</t>
+  </si>
+  <si>
+    <t>CoinsDrop</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>SwordRarityDrop</t>
+  </si>
+  <si>
+    <t>PWDDrop</t>
   </si>
 </sst>
 </file>
@@ -363,10 +378,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -376,8 +391,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -387,8 +411,17 @@
       <c r="C2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -401,8 +434,19 @@
         <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <f>INT(D$2*(D$101/D$2)^(($A3-2)/99))</f>
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <f>INT(E$2*(E$101/E$2)^(($A3-2)/99))</f>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -415,8 +459,19 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <f t="shared" ref="D4:E67" si="2">INT(D$2*(D$101/D$2)^(($A4-2)/99))</f>
+        <v>52</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -429,8 +484,19 @@
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -443,8 +509,19 @@
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -457,8 +534,19 @@
         <f t="shared" si="1"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -471,8 +559,19 @@
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -485,8 +584,19 @@
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -499,8 +609,19 @@
         <f t="shared" si="1"/>
         <v>211</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -513,8 +634,19 @@
         <f t="shared" si="1"/>
         <v>236</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -527,8 +659,19 @@
         <f t="shared" si="1"/>
         <v>261</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -541,8 +684,19 @@
         <f t="shared" si="1"/>
         <v>286</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -555,8 +709,19 @@
         <f t="shared" si="1"/>
         <v>311</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -569,8 +734,19 @@
         <f t="shared" si="1"/>
         <v>336</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -583,8 +759,19 @@
         <f t="shared" si="1"/>
         <v>362</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -597,8 +784,19 @@
         <f t="shared" si="1"/>
         <v>387</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -611,8 +809,19 @@
         <f t="shared" si="1"/>
         <v>412</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>111</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -625,8 +834,19 @@
         <f t="shared" si="1"/>
         <v>437</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -639,8 +859,19 @@
         <f t="shared" si="1"/>
         <v>462</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>124</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -653,8 +884,19 @@
         <f t="shared" si="1"/>
         <v>487</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>131</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -667,8 +909,19 @@
         <f t="shared" si="1"/>
         <v>513</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -681,8 +934,19 @@
         <f t="shared" si="1"/>
         <v>538</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -695,8 +959,19 @@
         <f t="shared" si="1"/>
         <v>563</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -709,8 +984,19 @@
         <f t="shared" si="1"/>
         <v>588</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -723,8 +1009,19 @@
         <f t="shared" si="1"/>
         <v>613</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -737,8 +1034,19 @@
         <f t="shared" si="1"/>
         <v>638</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -751,8 +1059,19 @@
         <f t="shared" si="1"/>
         <v>663</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -765,8 +1084,19 @@
         <f t="shared" si="1"/>
         <v>689</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <f t="shared" si="2"/>
+        <v>201</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -779,8 +1109,19 @@
         <f t="shared" si="1"/>
         <v>714</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <f t="shared" si="2"/>
+        <v>212</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -793,8 +1134,19 @@
         <f t="shared" si="1"/>
         <v>739</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <f t="shared" si="2"/>
+        <v>223</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -807,8 +1159,19 @@
         <f t="shared" si="1"/>
         <v>764</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -821,8 +1184,19 @@
         <f t="shared" si="1"/>
         <v>789</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>249</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -835,8 +1209,19 @@
         <f t="shared" si="1"/>
         <v>814</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>262</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -849,8 +1234,19 @@
         <f t="shared" si="1"/>
         <v>840</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>277</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -863,8 +1259,19 @@
         <f t="shared" si="1"/>
         <v>865</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>292</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -877,8 +1284,19 @@
         <f t="shared" si="1"/>
         <v>890</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>308</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -891,8 +1309,19 @@
         <f t="shared" si="1"/>
         <v>915</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>325</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -905,8 +1334,19 @@
         <f t="shared" si="1"/>
         <v>940</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <f t="shared" si="2"/>
+        <v>343</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -919,8 +1359,19 @@
         <f t="shared" si="1"/>
         <v>965</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <f t="shared" si="2"/>
+        <v>362</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -933,8 +1384,19 @@
         <f t="shared" si="1"/>
         <v>990</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <f t="shared" si="2"/>
+        <v>382</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="F41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -947,8 +1409,19 @@
         <f t="shared" si="1"/>
         <v>1016</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <f t="shared" si="2"/>
+        <v>403</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="F42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -961,8 +1434,19 @@
         <f t="shared" si="1"/>
         <v>1041</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <f t="shared" si="2"/>
+        <v>425</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="F43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -975,8 +1459,19 @@
         <f t="shared" si="1"/>
         <v>1066</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44">
+        <f t="shared" si="2"/>
+        <v>448</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="F44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -989,8 +1484,19 @@
         <f t="shared" si="1"/>
         <v>1091</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <f t="shared" si="2"/>
+        <v>473</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="F45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1003,8 +1509,19 @@
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46">
+        <f t="shared" si="2"/>
+        <v>499</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="F46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1017,8 +1534,19 @@
         <f t="shared" si="1"/>
         <v>1141</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47">
+        <f t="shared" si="2"/>
+        <v>526</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="F47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1031,8 +1559,19 @@
         <f t="shared" si="1"/>
         <v>1166</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48">
+        <f t="shared" si="2"/>
+        <v>555</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="F48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -1045,8 +1584,19 @@
         <f t="shared" si="1"/>
         <v>1192</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49">
+        <f t="shared" si="2"/>
+        <v>586</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="F49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -1059,8 +1609,19 @@
         <f t="shared" si="1"/>
         <v>1217</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50">
+        <f t="shared" si="2"/>
+        <v>618</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="F50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -1073,8 +1634,19 @@
         <f t="shared" si="1"/>
         <v>1242</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51">
+        <f t="shared" si="2"/>
+        <v>652</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="F51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -1087,8 +1659,19 @@
         <f t="shared" si="1"/>
         <v>1267</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <f t="shared" si="2"/>
+        <v>688</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="F52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -1101,8 +1684,19 @@
         <f t="shared" si="1"/>
         <v>1292</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53">
+        <f t="shared" si="2"/>
+        <v>726</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="2"/>
+        <v>114</v>
+      </c>
+      <c r="F53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -1115,8 +1709,19 @@
         <f t="shared" si="1"/>
         <v>1317</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54">
+        <f t="shared" si="2"/>
+        <v>766</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="F54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -1129,8 +1734,19 @@
         <f t="shared" si="1"/>
         <v>1343</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55">
+        <f t="shared" si="2"/>
+        <v>808</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="F55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -1143,8 +1759,19 @@
         <f t="shared" si="1"/>
         <v>1368</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56">
+        <f t="shared" si="2"/>
+        <v>852</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="F56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -1157,8 +1784,19 @@
         <f t="shared" si="1"/>
         <v>1393</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57">
+        <f t="shared" si="2"/>
+        <v>899</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+      <c r="F57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -1171,8 +1809,19 @@
         <f t="shared" si="1"/>
         <v>1418</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58">
+        <f t="shared" si="2"/>
+        <v>949</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="F58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -1185,8 +1834,19 @@
         <f t="shared" si="1"/>
         <v>1443</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59">
+        <f t="shared" si="2"/>
+        <v>1001</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="F59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -1199,8 +1859,19 @@
         <f t="shared" si="1"/>
         <v>1468</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60">
+        <f t="shared" si="2"/>
+        <v>1056</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="F60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -1213,8 +1884,19 @@
         <f t="shared" si="1"/>
         <v>1493</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="2"/>
+        <v>217</v>
+      </c>
+      <c r="F61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -1227,8 +1909,19 @@
         <f t="shared" si="1"/>
         <v>1519</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62">
+        <f t="shared" si="2"/>
+        <v>1175</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+      <c r="F62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1241,8 +1934,19 @@
         <f t="shared" si="1"/>
         <v>1544</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63">
+        <f t="shared" si="2"/>
+        <v>1240</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="2"/>
+        <v>256</v>
+      </c>
+      <c r="F63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -1255,8 +1959,19 @@
         <f t="shared" si="1"/>
         <v>1569</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64">
+        <f t="shared" si="2"/>
+        <v>1308</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="2"/>
+        <v>277</v>
+      </c>
+      <c r="F64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -1269,8 +1984,19 @@
         <f t="shared" si="1"/>
         <v>1594</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65">
+        <f t="shared" si="2"/>
+        <v>1380</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="2"/>
+        <v>301</v>
+      </c>
+      <c r="F65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -1283,8 +2009,19 @@
         <f t="shared" si="1"/>
         <v>1619</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66">
+        <f t="shared" si="2"/>
+        <v>1456</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="2"/>
+        <v>326</v>
+      </c>
+      <c r="F66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -1297,472 +2034,846 @@
         <f t="shared" si="1"/>
         <v>1644</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67">
+        <f t="shared" si="2"/>
+        <v>1536</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="2"/>
+        <v>353</v>
+      </c>
+      <c r="F67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
-        <f t="shared" ref="A68:A101" si="2">A67+1</f>
+        <f t="shared" ref="A68:A101" si="3">A67+1</f>
         <v>67</v>
       </c>
       <c r="B68">
-        <f t="shared" ref="B68:C100" si="3">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B68:C100" si="4">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
         <v>16683</v>
       </c>
       <c r="C68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1670</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68">
+        <f t="shared" ref="D68:E100" si="5">INT(D$2*(D$101/D$2)^(($A68-2)/99))</f>
+        <v>1620</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="5"/>
+        <v>383</v>
+      </c>
+      <c r="F68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>68</v>
       </c>
       <c r="B69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16935</v>
       </c>
       <c r="C69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1695</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69">
+        <f t="shared" si="5"/>
+        <v>1709</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="5"/>
+        <v>416</v>
+      </c>
+      <c r="F69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
       <c r="B70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17187</v>
       </c>
       <c r="C70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1720</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70">
+        <f t="shared" si="5"/>
+        <v>1803</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="5"/>
+        <v>451</v>
+      </c>
+      <c r="F70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="B71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17439</v>
       </c>
       <c r="C71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1745</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71">
+        <f t="shared" si="5"/>
+        <v>1903</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="5"/>
+        <v>489</v>
+      </c>
+      <c r="F71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="B72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17691</v>
       </c>
       <c r="C72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1770</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72">
+        <f t="shared" si="5"/>
+        <v>2007</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="5"/>
+        <v>530</v>
+      </c>
+      <c r="F72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="B73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17943</v>
       </c>
       <c r="C73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1795</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73">
+        <f t="shared" si="5"/>
+        <v>2118</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="5"/>
+        <v>574</v>
+      </c>
+      <c r="F73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>73</v>
       </c>
       <c r="B74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18195</v>
       </c>
       <c r="C74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1820</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74">
+        <f t="shared" si="5"/>
+        <v>2234</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="5"/>
+        <v>623</v>
+      </c>
+      <c r="F74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="B75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18447</v>
       </c>
       <c r="C75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1846</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75">
+        <f t="shared" si="5"/>
+        <v>2357</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="5"/>
+        <v>675</v>
+      </c>
+      <c r="F75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="B76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18699</v>
       </c>
       <c r="C76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1871</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76">
+        <f t="shared" si="5"/>
+        <v>2487</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="5"/>
+        <v>732</v>
+      </c>
+      <c r="F76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="B77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18951</v>
       </c>
       <c r="C77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1896</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77">
+        <f t="shared" si="5"/>
+        <v>2623</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="5"/>
+        <v>794</v>
+      </c>
+      <c r="F77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>77</v>
       </c>
       <c r="B78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19203</v>
       </c>
       <c r="C78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1921</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78">
+        <f t="shared" si="5"/>
+        <v>2768</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="5"/>
+        <v>861</v>
+      </c>
+      <c r="F78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
       <c r="B79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19455</v>
       </c>
       <c r="C79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1946</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79">
+        <f t="shared" si="5"/>
+        <v>2920</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="5"/>
+        <v>933</v>
+      </c>
+      <c r="F79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>79</v>
       </c>
       <c r="B80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19707</v>
       </c>
       <c r="C80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1971</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80">
+        <f t="shared" si="5"/>
+        <v>3080</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="5"/>
+        <v>1012</v>
+      </c>
+      <c r="F80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="B81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19959</v>
       </c>
       <c r="C81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1996</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81">
+        <f t="shared" si="5"/>
+        <v>3250</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="5"/>
+        <v>1097</v>
+      </c>
+      <c r="F81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="B82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20211</v>
       </c>
       <c r="C82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2022</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82">
+        <f t="shared" si="5"/>
+        <v>3428</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="5"/>
+        <v>1190</v>
+      </c>
+      <c r="F82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>82</v>
       </c>
       <c r="B83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20463</v>
       </c>
       <c r="C83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2047</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83">
+        <f t="shared" si="5"/>
+        <v>3617</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="5"/>
+        <v>1290</v>
+      </c>
+      <c r="F83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83</v>
       </c>
       <c r="B84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20715</v>
       </c>
       <c r="C84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2072</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84">
+        <f t="shared" si="5"/>
+        <v>3816</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="5"/>
+        <v>1399</v>
+      </c>
+      <c r="F84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="B85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20967</v>
       </c>
       <c r="C85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2097</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85">
+        <f t="shared" si="5"/>
+        <v>4025</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="5"/>
+        <v>1517</v>
+      </c>
+      <c r="F85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="B86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21219</v>
       </c>
       <c r="C86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2122</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86">
+        <f t="shared" si="5"/>
+        <v>4247</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="5"/>
+        <v>1645</v>
+      </c>
+      <c r="F86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>86</v>
       </c>
       <c r="B87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21471</v>
       </c>
       <c r="C87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2147</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87">
+        <f t="shared" si="5"/>
+        <v>4480</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="5"/>
+        <v>1783</v>
+      </c>
+      <c r="F87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="B88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21723</v>
       </c>
       <c r="C88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2173</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88">
+        <f t="shared" si="5"/>
+        <v>4727</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="5"/>
+        <v>1933</v>
+      </c>
+      <c r="F88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>88</v>
       </c>
       <c r="B89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21975</v>
       </c>
       <c r="C89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2198</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89">
+        <f t="shared" si="5"/>
+        <v>4987</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="5"/>
+        <v>2096</v>
+      </c>
+      <c r="F89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>89</v>
       </c>
       <c r="B90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22227</v>
       </c>
       <c r="C90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2223</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90">
+        <f t="shared" si="5"/>
+        <v>5261</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="5"/>
+        <v>2273</v>
+      </c>
+      <c r="F90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="B91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22479</v>
       </c>
       <c r="C91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2248</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91">
+        <f t="shared" si="5"/>
+        <v>5550</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="5"/>
+        <v>2464</v>
+      </c>
+      <c r="F91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91</v>
       </c>
       <c r="B92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22731</v>
       </c>
       <c r="C92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2273</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92">
+        <f t="shared" si="5"/>
+        <v>5855</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="5"/>
+        <v>2672</v>
+      </c>
+      <c r="F92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>92</v>
       </c>
       <c r="B93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22983</v>
       </c>
       <c r="C93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2298</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93">
+        <f t="shared" si="5"/>
+        <v>6177</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="5"/>
+        <v>2897</v>
+      </c>
+      <c r="F93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>93</v>
       </c>
       <c r="B94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23235</v>
       </c>
       <c r="C94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2323</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94">
+        <f t="shared" si="5"/>
+        <v>6517</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="5"/>
+        <v>3141</v>
+      </c>
+      <c r="F94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>94</v>
       </c>
       <c r="B95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23487</v>
       </c>
       <c r="C95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2349</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95">
+        <f t="shared" si="5"/>
+        <v>6875</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="5"/>
+        <v>3406</v>
+      </c>
+      <c r="F95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>95</v>
       </c>
       <c r="B96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23739</v>
       </c>
       <c r="C96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2374</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96">
+        <f t="shared" si="5"/>
+        <v>7253</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="5"/>
+        <v>3693</v>
+      </c>
+      <c r="F96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="B97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23991</v>
       </c>
       <c r="C97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2399</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97">
+        <f t="shared" si="5"/>
+        <v>7652</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="5"/>
+        <v>4004</v>
+      </c>
+      <c r="F97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>97</v>
       </c>
       <c r="B98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24243</v>
       </c>
       <c r="C98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2424</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98">
+        <f t="shared" si="5"/>
+        <v>8072</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="5"/>
+        <v>4341</v>
+      </c>
+      <c r="F98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="B99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24495</v>
       </c>
       <c r="C99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2449</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99">
+        <f t="shared" si="5"/>
+        <v>8516</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="5"/>
+        <v>4707</v>
+      </c>
+      <c r="F99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>99</v>
       </c>
       <c r="B100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24747</v>
       </c>
       <c r="C100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2474</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100">
+        <f t="shared" si="5"/>
+        <v>8984</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="5"/>
+        <v>5103</v>
+      </c>
+      <c r="F100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="B101">
@@ -1770,6 +2881,15 @@
       </c>
       <c r="C101">
         <v>2500</v>
+      </c>
+      <c r="D101">
+        <v>10000</v>
+      </c>
+      <c r="E101">
+        <v>6000</v>
+      </c>
+      <c r="F101" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1779,10 +2899,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CF0CBB-093D-4255-A489-4C757C3F6D8C}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1792,8 +2912,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1803,8 +2932,17 @@
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -1817,8 +2955,19 @@
         <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
         <v>351</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <f>INT(D$2*(D$101/D$2)^(($A3-2)/99))</f>
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <f>INT(E$2*(E$101/E$2)^(($A3-2)/99))</f>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -1831,8 +2980,19 @@
         <f t="shared" si="1"/>
         <v>603</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <f t="shared" ref="D4:E67" si="2">INT(D$2*(D$101/D$2)^(($A4-2)/99))</f>
+        <v>52</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1845,8 +3005,19 @@
         <f t="shared" si="1"/>
         <v>854</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1859,8 +3030,19 @@
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1873,8 +3055,19 @@
         <f t="shared" si="1"/>
         <v>1357</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1887,8 +3080,19 @@
         <f t="shared" si="1"/>
         <v>1609</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1901,8 +3105,19 @@
         <f t="shared" si="1"/>
         <v>1860</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1915,8 +3130,19 @@
         <f t="shared" si="1"/>
         <v>2112</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1929,8 +3155,19 @@
         <f t="shared" si="1"/>
         <v>2363</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1943,8 +3180,19 @@
         <f t="shared" si="1"/>
         <v>2615</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1957,8 +3205,19 @@
         <f t="shared" si="1"/>
         <v>2866</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1971,8 +3230,19 @@
         <f t="shared" si="1"/>
         <v>3118</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1985,8 +3255,19 @@
         <f t="shared" si="1"/>
         <v>3369</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1999,8 +3280,19 @@
         <f t="shared" si="1"/>
         <v>3621</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2013,8 +3305,19 @@
         <f t="shared" si="1"/>
         <v>3872</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2027,8 +3330,19 @@
         <f t="shared" si="1"/>
         <v>4124</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>111</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2041,8 +3355,19 @@
         <f t="shared" si="1"/>
         <v>4375</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2055,8 +3380,19 @@
         <f t="shared" si="1"/>
         <v>4627</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>124</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2069,8 +3405,19 @@
         <f t="shared" si="1"/>
         <v>4878</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>131</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2083,8 +3430,19 @@
         <f t="shared" si="1"/>
         <v>5130</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2097,8 +3455,19 @@
         <f t="shared" si="1"/>
         <v>5381</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2111,8 +3480,19 @@
         <f t="shared" si="1"/>
         <v>5633</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2125,8 +3505,19 @@
         <f t="shared" si="1"/>
         <v>5884</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2139,8 +3530,19 @@
         <f t="shared" si="1"/>
         <v>6136</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2153,8 +3555,19 @@
         <f t="shared" si="1"/>
         <v>6387</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2167,8 +3580,19 @@
         <f t="shared" si="1"/>
         <v>6639</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2181,8 +3605,19 @@
         <f t="shared" si="1"/>
         <v>6890</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <f t="shared" si="2"/>
+        <v>201</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2195,8 +3630,19 @@
         <f t="shared" si="1"/>
         <v>7142</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <f t="shared" si="2"/>
+        <v>212</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2209,8 +3655,19 @@
         <f t="shared" si="1"/>
         <v>7393</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <f t="shared" si="2"/>
+        <v>223</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2223,8 +3680,19 @@
         <f t="shared" si="1"/>
         <v>7645</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2237,8 +3705,19 @@
         <f t="shared" si="1"/>
         <v>7896</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>249</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2251,8 +3730,19 @@
         <f t="shared" si="1"/>
         <v>8148</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>262</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2265,8 +3755,19 @@
         <f t="shared" si="1"/>
         <v>8400</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>277</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2279,8 +3780,19 @@
         <f t="shared" si="1"/>
         <v>8651</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>292</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2293,8 +3805,19 @@
         <f t="shared" si="1"/>
         <v>8903</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>308</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2307,8 +3830,19 @@
         <f t="shared" si="1"/>
         <v>9154</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>325</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2321,8 +3855,19 @@
         <f t="shared" si="1"/>
         <v>9406</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <f t="shared" si="2"/>
+        <v>343</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2335,8 +3880,19 @@
         <f t="shared" si="1"/>
         <v>9657</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <f t="shared" si="2"/>
+        <v>362</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2349,8 +3905,19 @@
         <f t="shared" si="1"/>
         <v>9909</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <f t="shared" si="2"/>
+        <v>382</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="F41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2363,8 +3930,19 @@
         <f t="shared" si="1"/>
         <v>10160</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <f t="shared" si="2"/>
+        <v>403</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="F42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2377,8 +3955,19 @@
         <f t="shared" si="1"/>
         <v>10412</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <f t="shared" si="2"/>
+        <v>425</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="F43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2391,8 +3980,19 @@
         <f t="shared" si="1"/>
         <v>10663</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44">
+        <f t="shared" si="2"/>
+        <v>448</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="F44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2405,8 +4005,19 @@
         <f t="shared" si="1"/>
         <v>10915</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <f t="shared" si="2"/>
+        <v>473</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="F45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -2419,8 +4030,19 @@
         <f t="shared" si="1"/>
         <v>11166</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46">
+        <f t="shared" si="2"/>
+        <v>499</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="F46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -2433,8 +4055,19 @@
         <f t="shared" si="1"/>
         <v>11418</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47">
+        <f t="shared" si="2"/>
+        <v>526</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="F47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -2447,8 +4080,19 @@
         <f t="shared" si="1"/>
         <v>11669</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48">
+        <f t="shared" si="2"/>
+        <v>555</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="F48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2461,8 +4105,19 @@
         <f t="shared" si="1"/>
         <v>11921</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49">
+        <f t="shared" si="2"/>
+        <v>586</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="F49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2475,8 +4130,19 @@
         <f t="shared" si="1"/>
         <v>12172</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50">
+        <f t="shared" si="2"/>
+        <v>618</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="F50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2489,8 +4155,19 @@
         <f t="shared" si="1"/>
         <v>12424</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51">
+        <f t="shared" si="2"/>
+        <v>652</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="F51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -2503,8 +4180,19 @@
         <f t="shared" si="1"/>
         <v>12675</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <f t="shared" si="2"/>
+        <v>688</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="F52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -2517,8 +4205,19 @@
         <f t="shared" si="1"/>
         <v>12927</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53">
+        <f t="shared" si="2"/>
+        <v>726</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="2"/>
+        <v>114</v>
+      </c>
+      <c r="F53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -2531,8 +4230,19 @@
         <f t="shared" si="1"/>
         <v>13178</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54">
+        <f t="shared" si="2"/>
+        <v>766</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="F54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -2545,8 +4255,19 @@
         <f t="shared" si="1"/>
         <v>13430</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55">
+        <f t="shared" si="2"/>
+        <v>808</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="F55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -2559,8 +4280,19 @@
         <f t="shared" si="1"/>
         <v>13681</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56">
+        <f t="shared" si="2"/>
+        <v>852</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="F56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -2573,8 +4305,19 @@
         <f t="shared" si="1"/>
         <v>13933</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57">
+        <f t="shared" si="2"/>
+        <v>899</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+      <c r="F57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -2587,8 +4330,19 @@
         <f t="shared" si="1"/>
         <v>14184</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58">
+        <f t="shared" si="2"/>
+        <v>949</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="F58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -2601,8 +4355,19 @@
         <f t="shared" si="1"/>
         <v>14436</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59">
+        <f t="shared" si="2"/>
+        <v>1001</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="F59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -2615,8 +4380,19 @@
         <f t="shared" si="1"/>
         <v>14687</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60">
+        <f t="shared" si="2"/>
+        <v>1056</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="F60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -2629,8 +4405,19 @@
         <f t="shared" si="1"/>
         <v>14939</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61">
+        <f t="shared" si="2"/>
+        <v>1114</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="2"/>
+        <v>217</v>
+      </c>
+      <c r="F61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -2643,8 +4430,19 @@
         <f t="shared" si="1"/>
         <v>15190</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62">
+        <f t="shared" si="2"/>
+        <v>1175</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+      <c r="F62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -2657,8 +4455,19 @@
         <f t="shared" si="1"/>
         <v>15442</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63">
+        <f t="shared" si="2"/>
+        <v>1240</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="2"/>
+        <v>256</v>
+      </c>
+      <c r="F63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -2671,8 +4480,19 @@
         <f t="shared" si="1"/>
         <v>15693</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64">
+        <f t="shared" si="2"/>
+        <v>1308</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="2"/>
+        <v>277</v>
+      </c>
+      <c r="F64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -2685,8 +4505,19 @@
         <f t="shared" si="1"/>
         <v>15945</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65">
+        <f t="shared" si="2"/>
+        <v>1380</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="2"/>
+        <v>301</v>
+      </c>
+      <c r="F65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -2699,8 +4530,19 @@
         <f t="shared" si="1"/>
         <v>16196</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66">
+        <f t="shared" si="2"/>
+        <v>1456</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="2"/>
+        <v>326</v>
+      </c>
+      <c r="F66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -2713,472 +4555,846 @@
         <f t="shared" si="1"/>
         <v>16448</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67">
+        <f t="shared" si="2"/>
+        <v>1536</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="2"/>
+        <v>353</v>
+      </c>
+      <c r="F67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
-        <f t="shared" ref="A68:A101" si="2">A67+1</f>
+        <f t="shared" ref="A68:A101" si="3">A67+1</f>
         <v>67</v>
       </c>
       <c r="B68">
-        <f t="shared" ref="B68:C100" si="3">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B68:C100" si="4">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
         <v>66833</v>
       </c>
       <c r="C68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16700</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68">
+        <f t="shared" ref="D68:E100" si="5">INT(D$2*(D$101/D$2)^(($A68-2)/99))</f>
+        <v>1620</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="5"/>
+        <v>383</v>
+      </c>
+      <c r="F68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>68</v>
       </c>
       <c r="B69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>67838</v>
       </c>
       <c r="C69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16951</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69">
+        <f t="shared" si="5"/>
+        <v>1709</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="5"/>
+        <v>416</v>
+      </c>
+      <c r="F69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
       <c r="B70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>68843</v>
       </c>
       <c r="C70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17203</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70">
+        <f t="shared" si="5"/>
+        <v>1803</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="5"/>
+        <v>451</v>
+      </c>
+      <c r="F70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="B71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>69848</v>
       </c>
       <c r="C71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17454</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71">
+        <f t="shared" si="5"/>
+        <v>1903</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="5"/>
+        <v>489</v>
+      </c>
+      <c r="F71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="B72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>70853</v>
       </c>
       <c r="C72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17706</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72">
+        <f t="shared" si="5"/>
+        <v>2007</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="5"/>
+        <v>530</v>
+      </c>
+      <c r="F72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="B73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>71858</v>
       </c>
       <c r="C73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17957</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73">
+        <f t="shared" si="5"/>
+        <v>2118</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="5"/>
+        <v>574</v>
+      </c>
+      <c r="F73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>73</v>
       </c>
       <c r="B74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>72863</v>
       </c>
       <c r="C74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18209</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74">
+        <f t="shared" si="5"/>
+        <v>2234</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="5"/>
+        <v>623</v>
+      </c>
+      <c r="F74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="B75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>73868</v>
       </c>
       <c r="C75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18460</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75">
+        <f t="shared" si="5"/>
+        <v>2357</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="5"/>
+        <v>675</v>
+      </c>
+      <c r="F75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="B76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>74873</v>
       </c>
       <c r="C76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18712</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76">
+        <f t="shared" si="5"/>
+        <v>2487</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="5"/>
+        <v>732</v>
+      </c>
+      <c r="F76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="B77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>75878</v>
       </c>
       <c r="C77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18963</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77">
+        <f t="shared" si="5"/>
+        <v>2623</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="5"/>
+        <v>794</v>
+      </c>
+      <c r="F77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>77</v>
       </c>
       <c r="B78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>76883</v>
       </c>
       <c r="C78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19215</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78">
+        <f t="shared" si="5"/>
+        <v>2768</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="5"/>
+        <v>861</v>
+      </c>
+      <c r="F78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
       <c r="B79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>77888</v>
       </c>
       <c r="C79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19466</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79">
+        <f t="shared" si="5"/>
+        <v>2920</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="5"/>
+        <v>933</v>
+      </c>
+      <c r="F79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>79</v>
       </c>
       <c r="B80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>78893</v>
       </c>
       <c r="C80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19718</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80">
+        <f t="shared" si="5"/>
+        <v>3080</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="5"/>
+        <v>1012</v>
+      </c>
+      <c r="F80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="B81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>79898</v>
       </c>
       <c r="C81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19969</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81">
+        <f t="shared" si="5"/>
+        <v>3250</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="5"/>
+        <v>1097</v>
+      </c>
+      <c r="F81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="B82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80904</v>
       </c>
       <c r="C82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20221</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82">
+        <f t="shared" si="5"/>
+        <v>3428</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="5"/>
+        <v>1190</v>
+      </c>
+      <c r="F82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>82</v>
       </c>
       <c r="B83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>81909</v>
       </c>
       <c r="C83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20472</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83">
+        <f t="shared" si="5"/>
+        <v>3617</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="5"/>
+        <v>1290</v>
+      </c>
+      <c r="F83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83</v>
       </c>
       <c r="B84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>82914</v>
       </c>
       <c r="C84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20724</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84">
+        <f t="shared" si="5"/>
+        <v>3816</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="5"/>
+        <v>1399</v>
+      </c>
+      <c r="F84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="B85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>83919</v>
       </c>
       <c r="C85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20975</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85">
+        <f t="shared" si="5"/>
+        <v>4025</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="5"/>
+        <v>1517</v>
+      </c>
+      <c r="F85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="B86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>84924</v>
       </c>
       <c r="C86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21227</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86">
+        <f t="shared" si="5"/>
+        <v>4247</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="5"/>
+        <v>1645</v>
+      </c>
+      <c r="F86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>86</v>
       </c>
       <c r="B87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>85929</v>
       </c>
       <c r="C87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21478</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87">
+        <f t="shared" si="5"/>
+        <v>4480</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="5"/>
+        <v>1783</v>
+      </c>
+      <c r="F87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="B88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>86934</v>
       </c>
       <c r="C88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21730</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88">
+        <f t="shared" si="5"/>
+        <v>4727</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="5"/>
+        <v>1933</v>
+      </c>
+      <c r="F88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>88</v>
       </c>
       <c r="B89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>87939</v>
       </c>
       <c r="C89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21981</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89">
+        <f t="shared" si="5"/>
+        <v>4987</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="5"/>
+        <v>2096</v>
+      </c>
+      <c r="F89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>89</v>
       </c>
       <c r="B90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>88944</v>
       </c>
       <c r="C90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22233</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90">
+        <f t="shared" si="5"/>
+        <v>5261</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="5"/>
+        <v>2273</v>
+      </c>
+      <c r="F90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="B91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>89949</v>
       </c>
       <c r="C91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22484</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91">
+        <f t="shared" si="5"/>
+        <v>5550</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="5"/>
+        <v>2464</v>
+      </c>
+      <c r="F91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91</v>
       </c>
       <c r="B92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>90954</v>
       </c>
       <c r="C92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22736</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92">
+        <f t="shared" si="5"/>
+        <v>5855</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="5"/>
+        <v>2672</v>
+      </c>
+      <c r="F92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>92</v>
       </c>
       <c r="B93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>91959</v>
       </c>
       <c r="C93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22987</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93">
+        <f t="shared" si="5"/>
+        <v>6177</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="5"/>
+        <v>2897</v>
+      </c>
+      <c r="F93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>93</v>
       </c>
       <c r="B94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>92964</v>
       </c>
       <c r="C94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23239</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94">
+        <f t="shared" si="5"/>
+        <v>6517</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="5"/>
+        <v>3141</v>
+      </c>
+      <c r="F94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>94</v>
       </c>
       <c r="B95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>93969</v>
       </c>
       <c r="C95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23490</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95">
+        <f t="shared" si="5"/>
+        <v>6875</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="5"/>
+        <v>3406</v>
+      </c>
+      <c r="F95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>95</v>
       </c>
       <c r="B96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>94974</v>
       </c>
       <c r="C96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23742</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96">
+        <f t="shared" si="5"/>
+        <v>7253</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="5"/>
+        <v>3693</v>
+      </c>
+      <c r="F96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="B97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>95979</v>
       </c>
       <c r="C97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23993</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97">
+        <f t="shared" si="5"/>
+        <v>7652</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="5"/>
+        <v>4004</v>
+      </c>
+      <c r="F97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>97</v>
       </c>
       <c r="B98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>96984</v>
       </c>
       <c r="C98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24245</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98">
+        <f t="shared" si="5"/>
+        <v>8072</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="5"/>
+        <v>4341</v>
+      </c>
+      <c r="F98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="B99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>97989</v>
       </c>
       <c r="C99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24496</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99">
+        <f t="shared" si="5"/>
+        <v>8516</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="5"/>
+        <v>4707</v>
+      </c>
+      <c r="F99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>99</v>
       </c>
       <c r="B100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>98994</v>
       </c>
       <c r="C100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24748</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100">
+        <f t="shared" si="5"/>
+        <v>8984</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="5"/>
+        <v>5103</v>
+      </c>
+      <c r="F100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="B101">
@@ -3186,6 +5402,15 @@
       </c>
       <c r="C101">
         <v>25000</v>
+      </c>
+      <c r="D101">
+        <v>10000</v>
+      </c>
+      <c r="E101">
+        <v>6000</v>
+      </c>
+      <c r="F101" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
